--- a/files/港岛-半山区东部-Central Peak I.xlsx
+++ b/files/港岛-半山区东部-Central Peak I.xlsx
@@ -8,11 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alpex I 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alpex II 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alpex III 销控表" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Everex I 销控表" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Everex II 销控表" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -115,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -180,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -196,51 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -812,7 +669,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-06</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -858,7 +715,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-07</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1350,7 +1207,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-01-04</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1396,7 +1253,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-01-04</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1792,7 +1649,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-06-14</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1838,7 +1695,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-10</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -3034,7 +2891,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-01-04</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3306,1284 +3163,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Central Peak I - Alpex I 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>10 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>5 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>MANOR A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>MANOR B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>SKY MANOR</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>SKYPLEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="16" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>SKYPLEX | 2785呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr"/>
-      <c r="C7" s="16" t="inlineStr"/>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>SKY MANOR | 2784呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>MANOR A | 2005呎 (4+房)
-$17,260万
-$86,085/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>MANOR B | 2080呎 (4+房)
-$16,380万
-$78,750/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr"/>
-      <c r="E8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>MANOR A | 2125呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>MANOR B | 2080呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr"/>
-      <c r="E9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>MANOR A | 2125呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>MANOR B | 1985呎 (3房)
-$15,600万
-$78,589/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr"/>
-      <c r="E10" s="16" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>MANOR A | 2109呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>MANOR B | 1985呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr"/>
-      <c r="E11" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Central Peak I - Alpex II 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>11 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>9 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>MANOR A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>MANOR B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>SKYPLEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>SKYPLEX | 2962呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>MANOR A | 2107呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>MANOR B | 2082呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>MANOR A | 1985呎 (4+房)
-$18,800万
-$94,710/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>MANOR B | 1985呎 (4+房)
-$17,600万
-$88,665/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>MANOR A | 1985呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>MANOR B | 1985呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>MANOR A | 1985呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>MANOR B | 1985呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>MANOR A | 2104呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>MANOR B | 2080呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Central Peak I - Alpex III 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>10 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>7 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>MANOR A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>MANOR B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>SKY MANOR</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>SKYPLEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="16" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>SKYPLEX | 2772呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr"/>
-      <c r="C7" s="16" t="inlineStr"/>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>SKY MANOR | 2627呎 (4+房)
-$28,800万
-$109,631/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>MANOR A | 2133呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>MANOR B | 2080呎 (4+房)
-$17,700万
-$85,096/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr"/>
-      <c r="E8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>MANOR A | 2013呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>MANOR B | 2080呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr"/>
-      <c r="E9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>MANOR A | 2133呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>MANOR B | 2080呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr"/>
-      <c r="E10" s="16" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>MANOR A | 2117呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>MANOR B | 2080呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr"/>
-      <c r="E11" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Central Peak I - Everex I 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>11 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>11 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>MANOR A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>MANOR B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>SKYPLEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>SKYPLEX | 2469呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>MANOR A | 1684呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>MANOR B | 1665呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>MANOR A | 1684呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>MANOR B | 1615呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>MANOR A | 1684呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>MANOR B | 1665呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>MANOR A | 1668呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>MANOR B | 1649呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>MANOR A | 1742呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>MANOR B | 1723呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Central Peak I - Everex II 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>11 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>8 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>MANOR A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>MANOR B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>SKYPLEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>SKYPLEX | 2469呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>MANOR A | 1684呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>MANOR B | 1665呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>MANOR A | 1684呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>MANOR B | 1615呎 (3房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>MANOR A | 1684呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>MANOR B | 1615呎 (3房)
-$12,920万
-$80,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>MANOR A | 1617呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>MANOR B | 1649呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>MANOR A | 1742呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>MANOR B | 1723呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-半山区东部-Central Peak I.xlsx
+++ b/files/港岛-半山区东部-Central Peak I.xlsx
@@ -8,6 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alpex I" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alpex II" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alpex III" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Everex I" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Everex II" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +46,102 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +152,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +217,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +233,63 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +666,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -3163,4 +3355,1284 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Alpex I 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>MANOR A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>MANOR B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>SKY MANOR</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>SKYPLEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>SKYPLEX | 2785呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>SKY MANOR | 2784呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>MANOR A | 2005呎 (4+房)
+$17260万
+$86,085/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>MANOR B | 2080呎 (4+房)
+$16380万
+$78,750/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>MANOR A | 2125呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>MANOR B | 2080呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>MANOR A | 2125呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>MANOR B | 1985呎 (3房)
+$15600万
+$78,589/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>MANOR A | 2109呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>MANOR B | 1985呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Alpex II 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>MANOR A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>MANOR B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>SKYPLEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>SKYPLEX | 2962呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>MANOR A | 2107呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>MANOR B | 2082呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>MANOR A | 1985呎 (4+房)
+$18800万
+$94,710/呎
+(21年-01月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>MANOR B | 1985呎 (4+房)
+$17600万
+$88,665/呎
+(21年-01月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>MANOR A | 1985呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>MANOR B | 1985呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>MANOR A | 1985呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>MANOR B | 1985呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>MANOR A | 2104呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>MANOR B | 2080呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Alpex III 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>MANOR A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>MANOR B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>SKY MANOR</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>SKYPLEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>SKYPLEX | 2772呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>SKY MANOR | 2627呎 (4+房)
+$28800万
+$109,631/呎
+(22年-06月)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>MANOR A | 2133呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>MANOR B | 2080呎 (4+房)
+$17700万
+$85,096/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>MANOR A | 2013呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>MANOR B | 2080呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>MANOR A | 2133呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>MANOR B | 2080呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>MANOR A | 2117呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>MANOR B | 2080呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Everex I 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>MANOR A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>MANOR B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>SKYPLEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>SKYPLEX | 2469呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>MANOR A | 1684呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>MANOR B | 1665呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>MANOR A | 1684呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>MANOR B | 1615呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>MANOR A | 1684呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>MANOR B | 1665呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>MANOR A | 1668呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>MANOR B | 1649呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>MANOR A | 1742呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>MANOR B | 1723呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Everex II 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>MANOR A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>MANOR B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>SKYPLEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>SKYPLEX | 2469呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>MANOR A | 1684呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>MANOR B | 1665呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>MANOR A | 1684呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>MANOR B | 1615呎 (3房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>MANOR A | 1684呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>MANOR B | 1615呎 (3房)
+$12920万
+$80,000/呎
+(21年-01月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>MANOR A | 1617呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>MANOR B | 1649呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>MANOR A | 1742呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>MANOR B | 1723呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-半山区东部-Central Peak I.xlsx
+++ b/files/港岛-半山区东部-Central Peak I.xlsx
@@ -666,7 +666,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-半山区东部-Central Peak I.xlsx
+++ b/files/港岛-半山区东部-Central Peak I.xlsx
@@ -656,7 +656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -669,6 +669,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -726,6 +730,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -776,6 +800,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -826,6 +870,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -872,6 +936,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -918,6 +1002,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -968,6 +1072,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1018,6 +1142,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1064,6 +1208,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1114,6 +1278,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1164,6 +1348,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1214,6 +1418,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1264,6 +1488,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1314,6 +1558,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1364,6 +1628,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1410,6 +1694,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1456,6 +1760,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1506,6 +1830,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1556,6 +1900,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1606,6 +1970,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1656,6 +2040,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1706,6 +2110,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1756,6 +2180,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1806,6 +2250,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1852,6 +2316,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1898,6 +2382,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1948,6 +2452,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1998,6 +2522,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2048,6 +2592,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2098,6 +2662,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2148,6 +2732,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2198,6 +2802,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2248,6 +2872,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2298,6 +2942,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2348,6 +3012,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2398,6 +3082,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2448,6 +3152,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2498,6 +3222,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2548,6 +3292,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2598,6 +3362,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2648,6 +3432,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2698,6 +3502,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2748,6 +3572,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2798,6 +3642,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2848,6 +3712,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2898,6 +3782,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2948,6 +3852,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2998,6 +3922,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3048,6 +3992,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3094,6 +4058,26 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3144,6 +4128,26 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3194,6 +4198,26 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3244,6 +4268,26 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3294,6 +4338,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3344,13 +4408,33 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -3518,7 +4602,7 @@
           <t>MANOR A | 2005呎 (4+房)
 $17260万
 $86,085/呎
-(20年-12月)</t>
+(20年-12月-07日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -3526,7 +4610,7 @@
           <t>MANOR B | 2080呎 (4+房)
 $16380万
 $78,750/呎
-(20年-12月)</t>
+(20年-12月-06日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -3576,7 +4660,7 @@
           <t>MANOR B | 1985呎 (3房)
 $15600万
 $78,589/呎
-(26年-01月)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr"/>
@@ -3776,7 +4860,7 @@
           <t>MANOR A | 1985呎 (4+房)
 $18800万
 $94,710/呎
-(21年-01月)</t>
+(21年-01月-04日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -3784,7 +4868,7 @@
           <t>MANOR B | 1985呎 (4+房)
 $17600万
 $88,665/呎
-(21年-01月)</t>
+(21年-01月-04日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -4015,7 +5099,7 @@
           <t>SKY MANOR | 2627呎 (4+房)
 $28800万
 $109,631/呎
-(22年-06月)</t>
+(22年-06月-14日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr"/>
@@ -4039,7 +5123,7 @@
           <t>MANOR B | 2080呎 (4+房)
 $17700万
 $85,096/呎
-(23年-04月)</t>
+(23年-04月-10日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -4575,7 +5659,7 @@
           <t>MANOR B | 1615呎 (3房)
 $12920万
 $80,000/呎
-(21年-01月)</t>
+(21年-01月-04日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>

--- a/files/港岛-半山区东部-Central Peak I.xlsx
+++ b/files/港岛-半山区东部-Central Peak I.xlsx
@@ -4602,7 +4602,7 @@
           <t>MANOR A | 2005呎 (4+房)
 $17260万
 $86,085/呎
-(20年-12月-07日)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -4610,7 +4610,7 @@
           <t>MANOR B | 2080呎 (4+房)
 $16380万
 $78,750/呎
-(20年-12月-06日)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -4660,7 +4660,7 @@
           <t>MANOR B | 1985呎 (3房)
 $15600万
 $78,589/呎
-(26年-01月-11日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr"/>
@@ -4860,7 +4860,7 @@
           <t>MANOR A | 1985呎 (4+房)
 $18800万
 $94,710/呎
-(21年-01月-04日)</t>
+(21年-01月)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -4868,7 +4868,7 @@
           <t>MANOR B | 1985呎 (4+房)
 $17600万
 $88,665/呎
-(21年-01月-04日)</t>
+(21年-01月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -5099,7 +5099,7 @@
           <t>SKY MANOR | 2627呎 (4+房)
 $28800万
 $109,631/呎
-(22年-06月-14日)</t>
+(22年-06月)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr"/>
@@ -5123,7 +5123,7 @@
           <t>MANOR B | 2080呎 (4+房)
 $17700万
 $85,096/呎
-(23年-04月-10日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -5659,7 +5659,7 @@
           <t>MANOR B | 1615呎 (3房)
 $12920万
 $80,000/呎
-(21年-01月-04日)</t>
+(21年-01月)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>

--- a/files/港岛-半山区东部-Central Peak I.xlsx
+++ b/files/港岛-半山区东部-Central Peak I.xlsx
@@ -4602,7 +4602,7 @@
           <t>MANOR A | 2005呎 (4+房)
 $17260万
 $86,085/呎
-(20年-12月)</t>
+(20年-12月-07日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -4610,7 +4610,7 @@
           <t>MANOR B | 2080呎 (4+房)
 $16380万
 $78,750/呎
-(20年-12月)</t>
+(20年-12月-06日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -4660,7 +4660,7 @@
           <t>MANOR B | 1985呎 (3房)
 $15600万
 $78,589/呎
-(26年-01月)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr"/>
@@ -4860,7 +4860,7 @@
           <t>MANOR A | 1985呎 (4+房)
 $18800万
 $94,710/呎
-(21年-01月)</t>
+(21年-01月-04日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -4868,7 +4868,7 @@
           <t>MANOR B | 1985呎 (4+房)
 $17600万
 $88,665/呎
-(21年-01月)</t>
+(21年-01月-04日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -5099,7 +5099,7 @@
           <t>SKY MANOR | 2627呎 (4+房)
 $28800万
 $109,631/呎
-(22年-06月)</t>
+(22年-06月-14日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr"/>
@@ -5123,7 +5123,7 @@
           <t>MANOR B | 2080呎 (4+房)
 $17700万
 $85,096/呎
-(23年-04月)</t>
+(23年-04月-10日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -5659,7 +5659,7 @@
           <t>MANOR B | 1615呎 (3房)
 $12920万
 $80,000/呎
-(21年-01月)</t>
+(21年-01月-04日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>
